--- a/output/graficos_dimensiones/comunal_d_env_a_2018_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:14</t>
+    <t xml:space="preserve">2026-09-10 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:28</t>
+    <t xml:space="preserve">2026-09-12 22:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_maule.xlsx
@@ -45,12 +45,12 @@
     <t xml:space="preserve">Pencahue</t>
   </si>
   <si>
+    <t xml:space="preserve">Pelluhue</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vichuquén</t>
   </si>
   <si>
-    <t xml:space="preserve">Pelluhue</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pelarco</t>
   </si>
   <si>
@@ -72,12 +72,12 @@
     <t xml:space="preserve">Retiro</t>
   </si>
   <si>
+    <t xml:space="preserve">Longaví</t>
+  </si>
+  <si>
     <t xml:space="preserve">Río Claro</t>
   </si>
   <si>
-    <t xml:space="preserve">Longaví</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rauco</t>
   </si>
   <si>
@@ -99,24 +99,24 @@
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
+    <t xml:space="preserve">Linares</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
-    <t xml:space="preserve">Linares</t>
-  </si>
-  <si>
     <t xml:space="preserve">Talca</t>
   </si>
   <si>
     <t xml:space="preserve">Molina</t>
   </si>
   <si>
+    <t xml:space="preserve">Yerbas Buenas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Empedrado</t>
   </si>
   <si>
-    <t xml:space="preserve">Yerbas Buenas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curicó</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:39</t>
+    <t xml:space="preserve">2026-09-24 00:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -565,7 +565,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>171.93</v>
+        <v>185.09</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>135.85</v>
+        <v>147.13</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>133.59</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="5">
@@ -610,13 +610,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7309</v>
+        <v>7203</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>129.61</v>
+        <v>138.58</v>
       </c>
     </row>
     <row r="6">
@@ -627,13 +627,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7203</v>
+        <v>7309</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>127.82</v>
+        <v>137.77</v>
       </c>
     </row>
     <row r="7">
@@ -650,7 +650,7 @@
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>119</v>
+        <v>125.7</v>
       </c>
     </row>
     <row r="8">
@@ -667,7 +667,7 @@
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>114.21</v>
+        <v>122.64</v>
       </c>
     </row>
     <row r="9">
@@ -684,7 +684,7 @@
         <v>2018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>112.41</v>
+        <v>121.04</v>
       </c>
     </row>
     <row r="10">
@@ -701,7 +701,7 @@
         <v>2018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>110.34</v>
+        <v>119.11</v>
       </c>
     </row>
     <row r="11">
@@ -718,7 +718,7 @@
         <v>2018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>107.85</v>
+        <v>116.84</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         <v>2018</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>103.42</v>
+        <v>110.39</v>
       </c>
     </row>
     <row r="13">
@@ -752,7 +752,7 @@
         <v>2018</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>101.89</v>
+        <v>108.95</v>
       </c>
     </row>
     <row r="14">
@@ -763,13 +763,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7108</v>
+        <v>7403</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>99.82</v>
+        <v>106.95</v>
       </c>
     </row>
     <row r="15">
@@ -780,13 +780,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7403</v>
+        <v>7108</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>99.1</v>
+        <v>106.51</v>
       </c>
     </row>
     <row r="16">
@@ -803,7 +803,7 @@
         <v>2018</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>98.15</v>
+        <v>105.62</v>
       </c>
     </row>
     <row r="17">
@@ -820,7 +820,7 @@
         <v>2018</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>97.87</v>
+        <v>105.13</v>
       </c>
     </row>
     <row r="18">
@@ -837,7 +837,7 @@
         <v>2018</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>96.71</v>
+        <v>102.97</v>
       </c>
     </row>
     <row r="19">
@@ -854,7 +854,7 @@
         <v>2018</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>93.4</v>
+        <v>99.81</v>
       </c>
     </row>
     <row r="20">
@@ -871,7 +871,7 @@
         <v>2018</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>92.41</v>
+        <v>99.21</v>
       </c>
     </row>
     <row r="21">
@@ -888,7 +888,7 @@
         <v>2018</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>91.23</v>
+        <v>97.33</v>
       </c>
     </row>
     <row r="22">
@@ -905,7 +905,7 @@
         <v>2018</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>90.99</v>
+        <v>97.31</v>
       </c>
     </row>
     <row r="23">
@@ -916,13 +916,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7109</v>
+        <v>7401</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>89.1</v>
+        <v>95.67</v>
       </c>
     </row>
     <row r="24">
@@ -933,13 +933,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>7401</v>
+        <v>7109</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>89.04</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="25">
@@ -956,7 +956,7 @@
         <v>2018</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>88.7</v>
+        <v>95.48</v>
       </c>
     </row>
     <row r="26">
@@ -973,7 +973,7 @@
         <v>2018</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>87.46</v>
+        <v>93.52</v>
       </c>
     </row>
     <row r="27">
@@ -984,13 +984,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>7104</v>
+        <v>7408</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>86.52</v>
+        <v>93.01</v>
       </c>
     </row>
     <row r="28">
@@ -1001,13 +1001,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7408</v>
+        <v>7104</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>86.27</v>
+        <v>93.01</v>
       </c>
     </row>
     <row r="29">
@@ -1024,7 +1024,7 @@
         <v>2018</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>78.25</v>
+        <v>83.81</v>
       </c>
     </row>
     <row r="30">
@@ -1041,7 +1041,7 @@
         <v>2018</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>73.55</v>
+        <v>78.93</v>
       </c>
     </row>
     <row r="31">
@@ -1058,7 +1058,7 @@
         <v>2018</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>42.18</v>
+        <v>44.88</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:08</t>
+    <t xml:space="preserve">2026-10-02 15:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:39</t>
+    <t xml:space="preserve">2026-10-05 16:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
